--- a/public/template/template_import_saldo_awal.xlsx
+++ b/public/template/template_import_saldo_awal.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="saldo_jurnal" sheetId="1" state="visible" r:id="rId3"/>
@@ -13,6 +13,7 @@
     <sheet name="saldo_hutang" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="inventaris" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="bdd" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="saldo_stock_in_transit" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="54">
   <si>
     <t xml:space="preserve">account_code</t>
   </si>
@@ -159,20 +160,48 @@
   </si>
   <si>
     <t xml:space="preserve">Wifi Tumpang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no_invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUP PLASTIK 90ML 1,6GRAM HOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-00423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GELAS PLASTIK PP 18OZ OVAL 7GRAM HOK @50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SENDOK MAKAN HITAM SONE @100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLASTIK KANTONG PP 0.2x60x90 GAPURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO2512KD-00777</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="168" formatCode="@"/>
+    <numFmt numFmtId="169" formatCode="0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -198,6 +227,20 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -243,7 +286,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -289,6 +332,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4282,8 +4341,7 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.62"/>
   </cols>
@@ -4374,6 +4432,131 @@
       <c r="E5" s="1"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="51.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21.14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="n">
+        <v>1095</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="14" t="n">
+        <v>240</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>461405</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>1878829</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="n">
+        <v>2345</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>3063063</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="n">
+        <v>1469</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>924451</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
